--- a/V.xlsx
+++ b/V.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA139366-8D30-48CD-B77F-00B184B5D423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1812E1D2-9874-44CC-A934-5090748611FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50490" yWindow="680" windowWidth="24340" windowHeight="15680" xr2:uid="{D7A11B22-4522-467B-9402-0B9402DE3F95}"/>
+    <workbookView xWindow="20710" yWindow="10470" windowWidth="19890" windowHeight="10280" activeTab="1" xr2:uid="{D7A11B22-4522-467B-9402-0B9402DE3F95}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="100">
   <si>
     <t>Price</t>
   </si>
@@ -252,15 +252,6 @@
     <t>Total Transactions</t>
   </si>
   <si>
-    <t>International</t>
-  </si>
-  <si>
-    <t>Data Processing</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
     <t>APAC TPV</t>
   </si>
   <si>
@@ -328,6 +319,24 @@
   </si>
   <si>
     <t>Q325</t>
+  </si>
+  <si>
+    <t>FQ226</t>
+  </si>
+  <si>
+    <t>FQ326</t>
+  </si>
+  <si>
+    <t>FQ426</t>
+  </si>
+  <si>
+    <t>Data Processing (Transactions)</t>
+  </si>
+  <si>
+    <t>Service (Card Provider Fees)</t>
+  </si>
+  <si>
+    <t>International Transactions</t>
   </si>
 </sst>
 </file>
@@ -431,14 +440,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>47354</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>56426</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>47354</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>56426</xdr:colOff>
       <xdr:row>106</xdr:row>
       <xdr:rowOff>86254</xdr:rowOff>
     </xdr:to>
@@ -455,8 +464,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11921854" y="0"/>
-          <a:ext cx="0" cy="17225481"/>
+          <a:off x="13917569" y="0"/>
+          <a:ext cx="0" cy="17394540"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -821,7 +830,7 @@
         <v>2079</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
@@ -841,7 +850,7 @@
         <v>22986</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
@@ -852,7 +861,7 @@
         <v>25171</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
@@ -871,22 +880,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42FDF777-564E-431B-B3DF-DE9720FAF314}">
-  <dimension ref="A1:AJ103"/>
+  <dimension ref="A1:AM103"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="9" width="9.1796875" style="3"/>
     <col min="10" max="14" width="9.1796875" style="3" customWidth="1"/>
-    <col min="15" max="19" width="9.1796875" customWidth="1"/>
+    <col min="15" max="22" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:36" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -935,8 +944,19 @@
         <f>+O2+365</f>
         <v>46022</v>
       </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="T2" s="11">
+        <f>+S2+90</f>
+        <v>46112</v>
+      </c>
+      <c r="U2" s="11">
+        <v>46203</v>
+      </c>
+      <c r="V2" s="11">
+        <f>+U2+90</f>
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
@@ -956,105 +976,114 @@
         <v>13</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="Q3" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="R3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="U3">
+      <c r="V3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="X3">
         <v>2020</v>
       </c>
-      <c r="V3">
-        <f>+U3+1</f>
+      <c r="Y3">
+        <f>+X3+1</f>
         <v>2021</v>
       </c>
-      <c r="W3">
-        <f t="shared" ref="W3:AJ3" si="0">+V3+1</f>
+      <c r="Z3">
+        <f t="shared" ref="Z3:AM3" si="0">+Y3+1</f>
         <v>2022</v>
       </c>
-      <c r="X3">
+      <c r="AA3">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="Y3">
+      <c r="AB3">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="Z3">
+      <c r="AC3">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="AA3">
+      <c r="AD3">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="AB3">
+      <c r="AE3">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="AC3">
+      <c r="AF3">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="AD3">
+      <c r="AG3">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="AE3">
+      <c r="AH3">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="AF3">
+      <c r="AI3">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
-      <c r="AG3">
+      <c r="AJ3">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="AH3">
+      <c r="AK3">
         <f t="shared" si="0"/>
         <v>2033</v>
       </c>
-      <c r="AI3">
+      <c r="AL3">
         <f t="shared" si="0"/>
         <v>2034</v>
       </c>
-      <c r="AJ3">
+      <c r="AM3">
         <f t="shared" si="0"/>
         <v>2035</v>
       </c>
     </row>
-    <row r="4" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -1083,17 +1112,20 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
-      <c r="X4" s="2">
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="AA4" s="2">
         <v>2382</v>
       </c>
-      <c r="Y4" s="2">
-        <f t="shared" ref="Y4:Y9" si="1">SUM(L4:O4)</f>
+      <c r="AB4" s="2">
+        <f t="shared" ref="AB4:AB9" si="1">SUM(L4:O4)</f>
         <v>2330</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -1122,17 +1154,20 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
-      <c r="X5" s="2">
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="AA5" s="2">
         <v>422</v>
       </c>
-      <c r="Y5" s="2">
+      <c r="AB5" s="2">
         <f t="shared" si="1"/>
         <v>446</v>
       </c>
     </row>
-    <row r="6" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -1161,17 +1196,20 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
-      <c r="X6" s="2">
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="AA6" s="2">
         <v>1168</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="AB6" s="2">
         <f t="shared" si="1"/>
         <v>1272</v>
       </c>
     </row>
-    <row r="7" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1200,17 +1238,20 @@
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
-      <c r="X7" s="2">
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="AA7" s="2">
         <v>1389</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AB7" s="2">
         <f t="shared" si="1"/>
         <v>1445</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1239,17 +1280,20 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
-      <c r="X8" s="2">
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="AA8" s="2">
         <v>6824</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="AB8" s="2">
         <f t="shared" si="1"/>
         <v>7181</v>
       </c>
     </row>
-    <row r="9" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1278,17 +1322,20 @@
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
-      <c r="X9" s="2">
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="AA9" s="2">
         <v>2933</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="AB9" s="2">
         <f t="shared" si="1"/>
         <v>3239</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -1322,18 +1369,21 @@
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
-      <c r="X10" s="2">
-        <f>X11+X12</f>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="AA10" s="2">
+        <f>AA11+AA12</f>
         <v>15078</v>
       </c>
-      <c r="Y10" s="2">
-        <f>Y11+Y12</f>
+      <c r="AB10" s="2">
+        <f>AB11+AB12</f>
         <v>15917</v>
       </c>
     </row>
-    <row r="11" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -1362,17 +1412,20 @@
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
-      <c r="X11" s="2">
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="AA11" s="2">
         <v>6511</v>
       </c>
-      <c r="Y11" s="2">
+      <c r="AB11" s="2">
         <f>SUM(L11:O11)</f>
         <v>6866</v>
       </c>
     </row>
-    <row r="12" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -1401,22 +1454,28 @@
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
-      <c r="X12" s="2">
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="AA12" s="2">
         <v>8567</v>
       </c>
-      <c r="Y12" s="2">
+      <c r="AB12" s="2">
         <f>SUM(L12:O12)</f>
         <v>9051</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
-    </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+    </row>
+    <row r="14" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>68</v>
       </c>
@@ -1447,15 +1506,18 @@
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
-      <c r="X14" s="2">
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="AA14" s="2">
         <v>96422</v>
       </c>
-      <c r="Y14" s="2">
+      <c r="AB14" s="2">
         <f>SUM(L14:O14)</f>
         <v>106492</v>
       </c>
     </row>
-    <row r="15" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>69</v>
       </c>
@@ -1486,15 +1548,18 @@
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
-      <c r="X15" s="2">
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="AA15" s="2">
         <v>170276</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="AB15" s="2">
         <f>SUM(L15:O15)</f>
         <v>186975</v>
       </c>
     </row>
-    <row r="16" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>70</v>
       </c>
@@ -1530,16 +1595,19 @@
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
-      <c r="X16" s="2">
-        <f>+X14+X15</f>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="AA16" s="2">
+        <f>+AA14+AA15</f>
         <v>266698</v>
       </c>
-      <c r="Y16" s="2">
-        <f>+Y15+Y14</f>
+      <c r="AB16" s="2">
+        <f>+AB15+AB14</f>
         <v>293467</v>
       </c>
     </row>
-    <row r="17" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -1557,10 +1625,13 @@
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
-    </row>
-    <row r="18" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+    </row>
+    <row r="18" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -1587,13 +1658,16 @@
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
-      <c r="X18" s="2">
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="AA18" s="2">
         <v>3986</v>
       </c>
     </row>
-    <row r="19" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -1620,20 +1694,26 @@
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
-      <c r="X19" s="2">
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="AA19" s="2">
         <v>4481</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+    </row>
+    <row r="21" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -1666,14 +1746,29 @@
       <c r="O21" s="5">
         <v>4208</v>
       </c>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-    </row>
-    <row r="22" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P21" s="5">
+        <v>4399</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>4330</v>
+      </c>
+      <c r="R21" s="5">
+        <v>4602</v>
+      </c>
+      <c r="S21" s="5">
+        <v>4760</v>
+      </c>
+      <c r="T21" s="5">
+        <v>4981</v>
+      </c>
+      <c r="U21" s="5">
+        <v>4922</v>
+      </c>
+      <c r="V21" s="5"/>
+    </row>
+    <row r="22" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -1706,14 +1801,29 @@
       <c r="O22" s="5">
         <v>4745</v>
       </c>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-    </row>
-    <row r="23" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P22" s="5">
+        <v>4701</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>5153</v>
+      </c>
+      <c r="R22" s="5">
+        <v>5394</v>
+      </c>
+      <c r="S22" s="5">
+        <v>5544</v>
+      </c>
+      <c r="T22" s="5">
+        <v>5543</v>
+      </c>
+      <c r="U22" s="5">
+        <v>6042</v>
+      </c>
+      <c r="V22" s="5"/>
+    </row>
+    <row r="23" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -1746,12 +1856,27 @@
       <c r="O23" s="5">
         <v>3442</v>
       </c>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-    </row>
-    <row r="24" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P23" s="5">
+        <v>3291</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>3633</v>
+      </c>
+      <c r="R23" s="5">
+        <v>3800</v>
+      </c>
+      <c r="S23" s="5">
+        <v>3652</v>
+      </c>
+      <c r="T23" s="5">
+        <v>3631</v>
+      </c>
+      <c r="U23" s="5">
+        <v>3853</v>
+      </c>
+      <c r="V23" s="5"/>
+    </row>
+    <row r="24" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
@@ -1786,12 +1911,27 @@
       <c r="O24" s="5">
         <v>912</v>
       </c>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-    </row>
-    <row r="25" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="5">
+        <v>937</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>1028</v>
+      </c>
+      <c r="R24" s="5">
+        <v>1176</v>
+      </c>
+      <c r="S24" s="5">
+        <v>1214</v>
+      </c>
+      <c r="T24" s="5">
+        <v>1320</v>
+      </c>
+      <c r="U24" s="5">
+        <v>1496</v>
+      </c>
+      <c r="V24" s="5"/>
+    </row>
+    <row r="25" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>31</v>
       </c>
@@ -1826,12 +1966,27 @@
       <c r="O25" s="5">
         <v>-3797</v>
       </c>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-    </row>
-    <row r="26" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P25" s="5">
+        <v>-3734</v>
+      </c>
+      <c r="Q25" s="5">
+        <v>-3972</v>
+      </c>
+      <c r="R25" s="5">
+        <v>-4248</v>
+      </c>
+      <c r="S25" s="5">
+        <v>-4269</v>
+      </c>
+      <c r="T25" s="5">
+        <v>-4245</v>
+      </c>
+      <c r="U25" s="5">
+        <v>-4680</v>
+      </c>
+      <c r="V25" s="5"/>
+    </row>
+    <row r="26" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -1849,8 +2004,11 @@
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
-    </row>
-    <row r="27" spans="2:24" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+    </row>
+    <row r="27" spans="2:27" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
         <v>7</v>
       </c>
@@ -1861,7 +2019,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="6">
-        <f t="shared" ref="G27:S27" si="5">SUM(G21:G25)</f>
+        <f t="shared" ref="G27:U27" si="5">SUM(G21:G25)</f>
         <v>7936</v>
       </c>
       <c r="H27" s="6">
@@ -1897,20 +2055,31 @@
         <v>9510</v>
       </c>
       <c r="P27" s="6">
+        <f t="shared" si="5"/>
         <v>9594</v>
       </c>
       <c r="Q27" s="6">
+        <f t="shared" si="5"/>
         <v>10172</v>
       </c>
       <c r="R27" s="6">
+        <f t="shared" si="5"/>
         <v>10724</v>
       </c>
       <c r="S27" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>10901</v>
+      </c>
+      <c r="T27" s="6">
+        <f t="shared" si="5"/>
+        <v>11230</v>
+      </c>
+      <c r="U27" s="6">
+        <f t="shared" si="5"/>
+        <v>11633</v>
+      </c>
+    </row>
+    <row r="28" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>15</v>
       </c>
@@ -1957,7 +2126,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="29" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
@@ -2017,7 +2186,7 @@
         <v>10485</v>
       </c>
     </row>
-    <row r="30" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>20</v>
       </c>
@@ -2064,7 +2233,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="31" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>19</v>
       </c>
@@ -2111,7 +2280,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="32" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>18</v>
       </c>
@@ -2158,7 +2327,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="33" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
         <v>17</v>
       </c>
@@ -2205,7 +2374,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="34" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>22</v>
       </c>
@@ -2271,8 +2440,11 @@
         <v>3118</v>
       </c>
       <c r="S34" s="5"/>
-    </row>
-    <row r="35" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+    </row>
+    <row r="35" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>21</v>
       </c>
@@ -2338,8 +2510,11 @@
         <v>7367</v>
       </c>
       <c r="S35" s="5"/>
-    </row>
-    <row r="36" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+    </row>
+    <row r="36" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>27</v>
       </c>
@@ -2389,7 +2564,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>26</v>
       </c>
@@ -2455,8 +2630,11 @@
         <v>7442</v>
       </c>
       <c r="S37" s="5"/>
-    </row>
-    <row r="38" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+    </row>
+    <row r="38" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>25</v>
       </c>
@@ -2503,7 +2681,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="39" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
         <v>24</v>
       </c>
@@ -2569,7 +2747,7 @@
         <v>6309</v>
       </c>
     </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>23</v>
       </c>
@@ -2626,8 +2804,11 @@
         <v>3.0346320346320348</v>
       </c>
       <c r="S40" s="1"/>
-    </row>
-    <row r="41" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+    </row>
+    <row r="41" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -2687,47 +2868,50 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>14</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4">
-        <f>+K27/G27-1</f>
+        <f t="shared" ref="K43:R43" si="20">+K27/G27-1</f>
         <v>8.7953629032258007E-2</v>
       </c>
       <c r="L43" s="4">
-        <f>+L27/H27-1</f>
+        <f t="shared" si="20"/>
         <v>9.8935504070131408E-2</v>
       </c>
       <c r="M43" s="4">
-        <f>+M27/I27-1</f>
+        <f t="shared" si="20"/>
         <v>9.5654314908285132E-2</v>
       </c>
       <c r="N43" s="4">
-        <f>+N27/J27-1</f>
+        <f t="shared" si="20"/>
         <v>0.11708676965965847</v>
       </c>
       <c r="O43" s="4">
-        <f>+O27/K27-1</f>
+        <f t="shared" si="20"/>
         <v>0.10145934676858936</v>
       </c>
       <c r="P43" s="4">
-        <f>+P27/L27-1</f>
+        <f t="shared" si="20"/>
         <v>9.3333333333333268E-2</v>
       </c>
       <c r="Q43" s="4">
-        <f>+Q27/M27-1</f>
+        <f t="shared" si="20"/>
         <v>0.14292134831460679</v>
       </c>
       <c r="R43" s="4">
-        <f>+R27/N27-1</f>
+        <f t="shared" si="20"/>
         <v>0.11510866174482692</v>
       </c>
       <c r="S43" s="4"/>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>66</v>
       </c>
@@ -2745,21 +2929,24 @@
         <v>0.11</v>
       </c>
       <c r="S44" s="4"/>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T44" s="4"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="4"/>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>16</v>
       </c>
       <c r="D45" s="4">
-        <f t="shared" ref="D45:F45" si="20">+D29/D27</f>
+        <f t="shared" ref="D45:F45" si="21">+D29/D27</f>
         <v>0.973570733064404</v>
       </c>
       <c r="E45" s="4" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F45" s="4" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G45" s="4">
@@ -2775,19 +2962,19 @@
         <v>0.97711697061215008</v>
       </c>
       <c r="J45" s="4">
-        <f t="shared" ref="J45:M45" si="21">+J29/J27</f>
+        <f t="shared" ref="J45:M45" si="22">+J29/J27</f>
         <v>0.97711697061215008</v>
       </c>
       <c r="K45" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.9790363678480426</v>
       </c>
       <c r="L45" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.97846153846153849</v>
       </c>
       <c r="M45" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.97752808988764039</v>
       </c>
       <c r="N45" s="4">
@@ -2811,29 +2998,32 @@
         <v>0.97771353972398356</v>
       </c>
       <c r="S45" s="4"/>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T45" s="4"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="4"/>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>21</v>
       </c>
       <c r="D46" s="4">
-        <f t="shared" ref="D46:F46" si="22">+D35/D27</f>
+        <f t="shared" ref="D46:F46" si="23">+D35/D27</f>
         <v>0.69675893726526639</v>
       </c>
       <c r="E46" s="4" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F46" s="4" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G46" s="4">
-        <f t="shared" ref="G46:K46" si="23">+G35/G27</f>
+        <f t="shared" ref="G46:K46" si="24">+G35/G27</f>
         <v>0.71295362903225812</v>
       </c>
       <c r="H46" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.69755792110206638</v>
       </c>
       <c r="I46" s="4">
@@ -2841,57 +3031,60 @@
         <v>0.68834940178882564</v>
       </c>
       <c r="J46" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.68834940178882564</v>
       </c>
       <c r="K46" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.71924947880472545</v>
       </c>
       <c r="L46" s="4">
-        <f>+L35/L27</f>
+        <f t="shared" ref="L46:R46" si="25">+L35/L27</f>
         <v>0.68421652421652424</v>
       </c>
       <c r="M46" s="4">
-        <f>+M35/M27</f>
+        <f t="shared" si="25"/>
         <v>0.69831460674157309</v>
       </c>
       <c r="N46" s="4">
-        <f>+N35/N27</f>
+        <f t="shared" si="25"/>
         <v>0.68971612769054802</v>
       </c>
       <c r="O46" s="4">
-        <f>+O35/O27</f>
+        <f t="shared" si="25"/>
         <v>0.68980021030494221</v>
       </c>
       <c r="P46" s="4">
-        <f>+P35/P27</f>
+        <f t="shared" si="25"/>
         <v>0.702522409839483</v>
       </c>
       <c r="Q46" s="4">
-        <f>+Q35/Q27</f>
+        <f t="shared" si="25"/>
         <v>0.69887927644514358</v>
       </c>
       <c r="R46" s="4">
-        <f>+R35/R27</f>
+        <f t="shared" si="25"/>
         <v>0.6869638194703469</v>
       </c>
       <c r="S46" s="4"/>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T46" s="4"/>
+      <c r="U46" s="4"/>
+      <c r="V46" s="4"/>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>46</v>
       </c>
       <c r="K47" s="4">
-        <f t="shared" ref="K47:M47" si="24">+K39/G39-1</f>
+        <f t="shared" ref="K47:M47" si="26">+K39/G39-1</f>
         <v>8.4053086159679768E-2</v>
       </c>
       <c r="L47" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.18303273213092863</v>
       </c>
       <c r="M47" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>6.2087458745874624E-2</v>
       </c>
       <c r="N47" s="4">
@@ -2906,62 +3099,68 @@
       <c r="Q47" s="4"/>
       <c r="R47" s="4"/>
       <c r="S47" s="4"/>
-    </row>
-    <row r="49" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T47" s="4"/>
+      <c r="U47" s="4"/>
+      <c r="V47" s="4"/>
+    </row>
+    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>44</v>
       </c>
       <c r="G49" s="5">
-        <f t="shared" ref="G49:R49" si="25">+G50-G67</f>
+        <f t="shared" ref="G49:R49" si="27">+G50-G67</f>
         <v>72</v>
       </c>
       <c r="H49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>444</v>
       </c>
       <c r="I49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1945</v>
       </c>
       <c r="J49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>3350</v>
       </c>
       <c r="K49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2318</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1776</v>
       </c>
       <c r="M49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>675</v>
       </c>
       <c r="N49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-27</v>
       </c>
       <c r="O49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-1406</v>
       </c>
       <c r="P49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="Q49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="R49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-2185</v>
       </c>
       <c r="S49" s="5"/>
-    </row>
-    <row r="50" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T49" s="5"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5"/>
+    </row>
+    <row r="50" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
         <v>3</v>
       </c>
@@ -3010,7 +3209,7 @@
         <v>22986</v>
       </c>
     </row>
-    <row r="51" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
         <v>28</v>
       </c>
@@ -3049,7 +3248,7 @@
         <v>4191</v>
       </c>
     </row>
-    <row r="52" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
         <v>29</v>
       </c>
@@ -3088,7 +3287,7 @@
         <v>3126</v>
       </c>
     </row>
-    <row r="53" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>30</v>
       </c>
@@ -3127,7 +3326,7 @@
         <v>3625</v>
       </c>
     </row>
-    <row r="54" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
         <v>31</v>
       </c>
@@ -3176,7 +3375,7 @@
         <v>7315</v>
       </c>
     </row>
-    <row r="55" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
         <v>32</v>
       </c>
@@ -3215,7 +3414,7 @@
         <v>2679</v>
       </c>
     </row>
-    <row r="56" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
         <v>33</v>
       </c>
@@ -3254,7 +3453,7 @@
         <v>4236</v>
       </c>
     </row>
-    <row r="57" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="2" t="s">
         <v>36</v>
       </c>
@@ -3303,7 +3502,7 @@
         <v>47525</v>
       </c>
     </row>
-    <row r="58" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>35</v>
       </c>
@@ -3342,7 +3541,7 @@
         <v>3944</v>
       </c>
     </row>
-    <row r="59" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
         <v>34</v>
       </c>
@@ -3351,56 +3550,59 @@
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5">
-        <f t="shared" ref="G59:R59" si="26">SUM(G50:G58)</f>
+        <f t="shared" ref="G59:R59" si="28">SUM(G50:G58)</f>
         <v>85387</v>
       </c>
       <c r="H59" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>86755</v>
       </c>
       <c r="I59" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>89234</v>
       </c>
       <c r="J59" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>90499</v>
       </c>
       <c r="K59" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>91409</v>
       </c>
       <c r="L59" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>92399</v>
       </c>
       <c r="M59" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>91040</v>
       </c>
       <c r="N59" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>94511</v>
       </c>
       <c r="O59" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>91888</v>
       </c>
       <c r="P59" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Q59" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="R59" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>99627</v>
       </c>
       <c r="S59" s="5"/>
-    </row>
-    <row r="60" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T59" s="5"/>
+      <c r="U59" s="5"/>
+      <c r="V59" s="5"/>
+    </row>
+    <row r="60" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
@@ -3414,7 +3616,7 @@
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
     </row>
-    <row r="61" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="2" t="s">
         <v>37</v>
       </c>
@@ -3453,7 +3655,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="62" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
         <v>38</v>
       </c>
@@ -3502,7 +3704,7 @@
         <v>7601</v>
       </c>
     </row>
-    <row r="63" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
         <v>30</v>
       </c>
@@ -3541,7 +3743,7 @@
         <v>3625</v>
       </c>
     </row>
-    <row r="64" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
         <v>39</v>
       </c>
@@ -3580,7 +3782,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="65" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
         <v>31</v>
       </c>
@@ -3619,7 +3821,7 @@
         <v>10369</v>
       </c>
     </row>
-    <row r="66" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
         <v>40</v>
       </c>
@@ -3658,7 +3860,7 @@
         <v>5466</v>
       </c>
     </row>
-    <row r="67" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
         <v>4</v>
       </c>
@@ -3699,7 +3901,7 @@
         <v>25171</v>
       </c>
     </row>
-    <row r="68" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
         <v>25</v>
       </c>
@@ -3738,7 +3940,7 @@
         <v>5549</v>
       </c>
     </row>
-    <row r="69" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
         <v>43</v>
       </c>
@@ -3777,7 +3979,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="70" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="s">
         <v>42</v>
       </c>
@@ -3816,7 +4018,7 @@
         <v>37909</v>
       </c>
     </row>
-    <row r="71" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
         <v>41</v>
       </c>
@@ -3825,56 +4027,59 @@
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
       <c r="G71" s="5">
-        <f t="shared" ref="G71:R71" si="27">SUM(G61:G70)</f>
+        <f t="shared" ref="G71:R71" si="29">SUM(G61:G70)</f>
         <v>85387</v>
       </c>
       <c r="H71" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>86755</v>
       </c>
       <c r="I71" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>89234</v>
       </c>
       <c r="J71" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>90499</v>
       </c>
       <c r="K71" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>91409</v>
       </c>
       <c r="L71" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>92399</v>
       </c>
       <c r="M71" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>91040</v>
       </c>
       <c r="N71" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>94511</v>
       </c>
       <c r="O71" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>91888</v>
       </c>
       <c r="P71" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Q71" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="R71" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>99627</v>
       </c>
       <c r="S71" s="5"/>
-    </row>
-    <row r="73" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T71" s="5"/>
+      <c r="U71" s="5"/>
+      <c r="V71" s="5"/>
+    </row>
+    <row r="73" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="2" t="s">
         <v>47</v>
       </c>
@@ -3883,55 +4088,55 @@
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="2">
-        <f t="shared" ref="G73:J73" si="28">G39</f>
+        <f t="shared" ref="G73:J73" si="30">G39</f>
         <v>4747</v>
       </c>
       <c r="H73" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>4491</v>
       </c>
       <c r="I73" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>4848</v>
       </c>
       <c r="J73" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>5057</v>
       </c>
       <c r="K73" s="2">
-        <f>K39</f>
+        <f t="shared" ref="K73:R73" si="31">K39</f>
         <v>5146</v>
       </c>
       <c r="L73" s="2">
-        <f>L39</f>
+        <f t="shared" si="31"/>
         <v>5313</v>
       </c>
       <c r="M73" s="2">
-        <f>M39</f>
+        <f t="shared" si="31"/>
         <v>5149</v>
       </c>
       <c r="N73" s="2">
-        <f>N39</f>
+        <f t="shared" si="31"/>
         <v>5602</v>
       </c>
       <c r="O73" s="2">
-        <f>O39</f>
+        <f t="shared" si="31"/>
         <v>5445</v>
       </c>
       <c r="P73" s="2">
-        <f>P39</f>
+        <f t="shared" si="31"/>
         <v>5882</v>
       </c>
       <c r="Q73" s="2">
-        <f>Q39</f>
+        <f t="shared" si="31"/>
         <v>6204</v>
       </c>
       <c r="R73" s="2">
-        <f>R39</f>
+        <f t="shared" si="31"/>
         <v>6309</v>
       </c>
     </row>
-    <row r="74" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="2" t="s">
         <v>48</v>
       </c>
@@ -3973,7 +4178,7 @@
         <v>5119</v>
       </c>
     </row>
-    <row r="75" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
         <v>31</v>
       </c>
@@ -4015,7 +4220,7 @@
         <v>3797</v>
       </c>
     </row>
-    <row r="76" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B76" s="2" t="s">
         <v>55</v>
       </c>
@@ -4057,7 +4262,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="77" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="2" t="s">
         <v>54</v>
       </c>
@@ -4099,7 +4304,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="78" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="2" t="s">
         <v>53</v>
       </c>
@@ -4141,7 +4346,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="2" t="s">
         <v>52</v>
       </c>
@@ -4183,7 +4388,7 @@
         <v>-27</v>
       </c>
     </row>
-    <row r="80" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="2" t="s">
         <v>51</v>
       </c>
@@ -4321,35 +4526,35 @@
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
       <c r="G83" s="2">
-        <f t="shared" ref="G83" si="29">SUM(G74:G82)</f>
+        <f t="shared" ref="G83" si="32">SUM(G74:G82)</f>
         <v>4171</v>
       </c>
       <c r="H83" s="2">
-        <f t="shared" ref="H83" si="30">SUM(H74:H82)</f>
+        <f t="shared" ref="H83" si="33">SUM(H74:H82)</f>
         <v>3860</v>
       </c>
       <c r="I83" s="2">
-        <f t="shared" ref="I83" si="31">SUM(I74:I82)</f>
+        <f t="shared" ref="I83" si="34">SUM(I74:I82)</f>
         <v>5797</v>
       </c>
       <c r="J83" s="2">
-        <f t="shared" ref="J83" si="32">SUM(J74:J82)</f>
+        <f t="shared" ref="J83" si="35">SUM(J74:J82)</f>
         <v>6927</v>
       </c>
       <c r="K83" s="2">
-        <f t="shared" ref="K83:N83" si="33">SUM(K74:K82)</f>
+        <f t="shared" ref="K83:N83" si="36">SUM(K74:K82)</f>
         <v>3614</v>
       </c>
       <c r="L83" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>4538</v>
       </c>
       <c r="M83" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>5134</v>
       </c>
       <c r="N83" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>6664</v>
       </c>
       <c r="O83" s="2">
@@ -4533,19 +4738,19 @@
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
       <c r="G89" s="2">
-        <f t="shared" ref="G89:J89" si="34">SUM(G85:G88)</f>
+        <f t="shared" ref="G89:J89" si="37">SUM(G85:G88)</f>
         <v>-510</v>
       </c>
       <c r="H89" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>-325</v>
       </c>
       <c r="I89" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>17</v>
       </c>
       <c r="J89" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>-1188</v>
       </c>
       <c r="K89" s="2">
@@ -4802,43 +5007,43 @@
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
       <c r="G96" s="2">
-        <f t="shared" ref="G96:O96" si="35">SUM(G91:G95)</f>
+        <f t="shared" ref="G96:O96" si="38">SUM(G91:G95)</f>
         <v>-6347</v>
       </c>
       <c r="H96" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>-2926</v>
       </c>
       <c r="I96" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>-3919</v>
       </c>
       <c r="J96" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>-4580</v>
       </c>
       <c r="K96" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>-4379</v>
       </c>
       <c r="L96" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>-3874</v>
       </c>
       <c r="M96" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>-5311</v>
       </c>
       <c r="N96" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>-7069</v>
       </c>
       <c r="O96" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>-5475</v>
       </c>
     </row>
-    <row r="97" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="2" t="s">
         <v>61</v>
       </c>
@@ -4880,7 +5085,7 @@
         <v>-508</v>
       </c>
     </row>
-    <row r="98" spans="2:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="2" t="s">
         <v>60</v>
       </c>
@@ -4889,45 +5094,45 @@
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="2">
-        <f t="shared" ref="G98:O98" si="36">+G97+G96+G89+G83</f>
+        <f t="shared" ref="G98:O98" si="39">+G97+G96+G89+G83</f>
         <v>-1994</v>
       </c>
       <c r="H98" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>745</v>
       </c>
       <c r="I98" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>1911</v>
       </c>
       <c r="J98" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>951</v>
       </c>
       <c r="K98" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>-2354</v>
       </c>
       <c r="L98" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>-688</v>
       </c>
       <c r="M98" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>328</v>
       </c>
       <c r="N98" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>487</v>
       </c>
       <c r="O98" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>203</v>
       </c>
     </row>
-    <row r="100" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B100" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G100" s="5">
         <f>+G83+G85</f>
@@ -4950,57 +5155,63 @@
         <v>3347</v>
       </c>
       <c r="L100" s="5">
-        <f t="shared" ref="L100:O100" si="37">+L83+L85</f>
+        <f t="shared" ref="L100:O100" si="40">+L83+L85</f>
         <v>4257</v>
       </c>
       <c r="M100" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>4734</v>
       </c>
       <c r="N100" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>6355</v>
       </c>
       <c r="O100" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>5051</v>
       </c>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
       <c r="R100" s="5"/>
       <c r="S100" s="5"/>
-    </row>
-    <row r="101" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T100" s="5"/>
+      <c r="U100" s="5"/>
+      <c r="V100" s="5"/>
+    </row>
+    <row r="101" spans="2:22" x14ac:dyDescent="0.25">
       <c r="J101" s="2">
-        <f t="shared" ref="J101:O101" si="38">SUM(G100:J100)</f>
+        <f t="shared" ref="J101:O101" si="41">SUM(G100:J100)</f>
         <v>19696</v>
       </c>
       <c r="K101" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>19121</v>
       </c>
       <c r="L101" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>19728</v>
       </c>
       <c r="M101" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>18960</v>
       </c>
       <c r="N101" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>18693</v>
       </c>
       <c r="O101" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>20397</v>
       </c>
       <c r="P101" s="2"/>
       <c r="Q101" s="2"/>
       <c r="R101" s="2"/>
       <c r="S101" s="2"/>
-    </row>
-    <row r="103" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T101" s="2"/>
+      <c r="U101" s="2"/>
+      <c r="V101" s="2"/>
+    </row>
+    <row r="103" spans="2:22" x14ac:dyDescent="0.25">
       <c r="J103" s="13"/>
       <c r="K103" s="13"/>
       <c r="L103" s="13"/>
@@ -5011,6 +5222,9 @@
       <c r="Q103" s="13"/>
       <c r="R103" s="13"/>
       <c r="S103" s="13"/>
+      <c r="T103" s="13"/>
+      <c r="U103" s="13"/>
+      <c r="V103" s="13"/>
     </row>
   </sheetData>
   <hyperlinks>
